--- a/exports/trend_1d/BAJAJ-AUTO_full_report.xlsx
+++ b/exports/trend_1d/BAJAJ-AUTO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.44</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>2291</v>
+        <v>2205</v>
       </c>
       <c r="I2" t="n">
         <v>2257.43070435</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.84</v>
+        <v>-6.49</v>
       </c>
       <c r="L2" t="n">
-        <v>3.84</v>
+        <v>6.68</v>
       </c>
       <c r="M2" t="n">
         <v>0.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.04</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42131</v>
+        <v>42132</v>
       </c>
       <c r="H3" t="n">
-        <v>2016.5</v>
+        <v>2070.5</v>
       </c>
       <c r="I3" t="n">
         <v>2045.456559549825</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="n">
-        <v>8.550000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="L3" t="n">
         <v>4.74</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.47</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42236</v>
+        <v>42237</v>
       </c>
       <c r="H4" t="n">
-        <v>2430</v>
+        <v>2346.5</v>
       </c>
       <c r="I4" t="n">
         <v>2372.715819391712</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K4" t="n">
-        <v>17.36</v>
+        <v>13.33</v>
       </c>
       <c r="L4" t="n">
         <v>3.45</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H5" t="n">
-        <v>2318</v>
+        <v>2391</v>
       </c>
       <c r="I5" t="n">
         <v>2361.842975266958</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K5" t="n">
-        <v>1.21</v>
+        <v>-1.9</v>
       </c>
       <c r="L5" t="n">
         <v>4.26</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>10.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>2369.5</v>
+        <v>2349.5</v>
       </c>
       <c r="I6" t="n">
         <v>2352.259147205872</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9</v>
+        <v>-1.74</v>
       </c>
       <c r="L6" t="n">
         <v>3.97</v>
       </c>
       <c r="M6" t="n">
-        <v>0.38</v>
+        <v>1.43</v>
       </c>
       <c r="N6" t="n">
         <v>4.62</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.3</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42418</v>
+        <v>42419</v>
       </c>
       <c r="H7" t="n">
-        <v>2347</v>
+        <v>2395</v>
       </c>
       <c r="I7" t="n">
         <v>2365.838478856938</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K7" t="n">
-        <v>0.11</v>
+        <v>-1.94</v>
       </c>
       <c r="L7" t="n">
         <v>5.75</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.81</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42425</v>
+        <v>42426</v>
       </c>
       <c r="H8" t="n">
-        <v>2264.5</v>
+        <v>2183</v>
       </c>
       <c r="I8" t="n">
         <v>2224.107273481817</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.45</v>
+        <v>-8.85</v>
       </c>
       <c r="L8" t="n">
-        <v>6.66</v>
+        <v>9.52</v>
       </c>
       <c r="M8" t="n">
         <v>0.39</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
         <v>2.05</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42458</v>
+        <v>42459</v>
       </c>
       <c r="H9" t="n">
-        <v>2294</v>
+        <v>2362.5</v>
       </c>
       <c r="I9" t="n">
         <v>2354.893715949249</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.08</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>6.14</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
         <v>1.19</v>
       </c>
       <c r="N9" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="O9" t="n">
         <v>-3.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.43</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H10" t="n">
-        <v>2842</v>
+        <v>2776</v>
       </c>
       <c r="I10" t="n">
         <v>2776.205830345871</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K10" t="n">
-        <v>20.3</v>
+        <v>17.5</v>
       </c>
       <c r="L10" t="n">
         <v>2.96</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.48</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42758</v>
+        <v>42759</v>
       </c>
       <c r="H11" t="n">
-        <v>2639.5</v>
+        <v>2730</v>
       </c>
       <c r="I11" t="n">
         <v>2673.20705522119</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K11" t="n">
-        <v>4.92</v>
+        <v>1.66</v>
       </c>
       <c r="L11" t="n">
         <v>3.78</v>
@@ -1068,7 +1199,7 @@
         <v>1.56</v>
       </c>
       <c r="N11" t="n">
-        <v>3.14</v>
+        <v>3.43</v>
       </c>
       <c r="O11" t="n">
         <v>-2.32</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.23</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42828</v>
+        <v>42830</v>
       </c>
       <c r="H12" t="n">
-        <v>2715</v>
+        <v>2692.5</v>
       </c>
       <c r="I12" t="n">
         <v>2711.071674264354</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.55</v>
+        <v>-1.37</v>
       </c>
       <c r="L12" t="n">
         <v>3.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.48</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H13" t="n">
-        <v>2826.5</v>
+        <v>2860.5</v>
       </c>
       <c r="I13" t="n">
         <v>2839.974687594766</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.98</v>
+        <v>-6.24</v>
       </c>
       <c r="L13" t="n">
-        <v>5.78</v>
+        <v>6.63</v>
       </c>
       <c r="M13" t="n">
         <v>0.98</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>2842</v>
+        <v>2755</v>
       </c>
       <c r="I14" t="n">
         <v>2794.691962564321</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.65</v>
+        <v>-3.69</v>
       </c>
       <c r="L14" t="n">
-        <v>3.34</v>
+        <v>4.13</v>
       </c>
       <c r="M14" t="n">
         <v>0.76</v>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42940</v>
+        <v>42941</v>
       </c>
       <c r="H15" t="n">
-        <v>2757</v>
+        <v>2777.5</v>
       </c>
       <c r="I15" t="n">
         <v>2772.505366423085</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="L15" t="n">
         <v>3.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.88</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42965</v>
+        <v>42968</v>
       </c>
       <c r="H16" t="n">
-        <v>2742</v>
+        <v>2698</v>
       </c>
       <c r="I16" t="n">
         <v>2702.965176016302</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.28</v>
+        <v>-2.86</v>
       </c>
       <c r="L16" t="n">
         <v>3.44</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H17" t="n">
-        <v>2745</v>
+        <v>2844.5</v>
       </c>
       <c r="I17" t="n">
         <v>2817.934372872741</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.74</v>
+        <v>-5.43</v>
       </c>
       <c r="L17" t="n">
-        <v>2.24</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
         <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
         <v>-1.6</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.58</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H18" t="n">
-        <v>3085.5</v>
+        <v>3032.5</v>
       </c>
       <c r="I18" t="n">
         <v>3071.488557143043</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" t="n">
-        <v>8.470000000000001</v>
+        <v>6.61</v>
       </c>
       <c r="L18" t="n">
         <v>3.04</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.95</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43090</v>
+        <v>43091</v>
       </c>
       <c r="H19" t="n">
-        <v>3208</v>
+        <v>3246.5</v>
       </c>
       <c r="I19" t="n">
         <v>3243.229407658449</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.79</v>
+        <v>-7.06</v>
       </c>
       <c r="L19" t="n">
-        <v>7.42</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
         <v>1.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>7.85</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43133</v>
+        <v>43136</v>
       </c>
       <c r="H20" t="n">
-        <v>3161</v>
+        <v>3107</v>
       </c>
       <c r="I20" t="n">
         <v>3109.942382260904</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.63</v>
+        <v>-4.3</v>
       </c>
       <c r="L20" t="n">
         <v>5.67</v>
       </c>
       <c r="M20" t="n">
-        <v>0.47</v>
+        <v>1.27</v>
       </c>
       <c r="N20" t="n">
         <v>5.03</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43216</v>
+        <v>43217</v>
       </c>
       <c r="H21" t="n">
-        <v>2813.5</v>
+        <v>2874.5</v>
       </c>
       <c r="I21" t="n">
         <v>2854.504647909622</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K21" t="n">
-        <v>9.449999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="L21" t="n">
         <v>1.48</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>6.07</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H22" t="n">
-        <v>2801</v>
+        <v>2757.5</v>
       </c>
       <c r="I22" t="n">
         <v>2758.765718223451</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.56</v>
+        <v>-4.07</v>
       </c>
       <c r="L22" t="n">
-        <v>2.78</v>
+        <v>4.31</v>
       </c>
       <c r="M22" t="n">
         <v>0.09</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>7.18</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43284</v>
+        <v>43285</v>
       </c>
       <c r="H23" t="n">
-        <v>2791.5</v>
+        <v>2905.5</v>
       </c>
       <c r="I23" t="n">
         <v>2836.027721393021</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.23</v>
+        <v>-5.37</v>
       </c>
       <c r="L23" t="n">
-        <v>3.95</v>
+        <v>5.71</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.91</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43300</v>
+        <v>43301</v>
       </c>
       <c r="H24" t="n">
-        <v>3038</v>
+        <v>2769.5</v>
       </c>
       <c r="I24" t="n">
         <v>2819.80150996301</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>4.56</v>
+        <v>-4.68</v>
       </c>
       <c r="L24" t="n">
-        <v>4.15</v>
+        <v>5.46</v>
       </c>
       <c r="M24" t="n">
         <v>1.48</v>
       </c>
       <c r="N24" t="n">
-        <v>2.06</v>
+        <v>8.84</v>
       </c>
       <c r="O24" t="n">
         <v>4.08</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>16.01</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43349</v>
+        <v>43350</v>
       </c>
       <c r="H25" t="n">
-        <v>2714.5</v>
+        <v>2851.5</v>
       </c>
       <c r="I25" t="n">
         <v>2759.618474564589</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>1.99</v>
+        <v>-2.96</v>
       </c>
       <c r="L25" t="n">
         <v>11.07</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="N25" t="n">
-        <v>2.77</v>
+        <v>5.05</v>
       </c>
       <c r="O25" t="n">
         <v>-8.84</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>7.6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H26" t="n">
-        <v>2714.5</v>
+        <v>2621</v>
       </c>
       <c r="I26" t="n">
         <v>2640.824155223892</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.8</v>
+        <v>-8.08</v>
       </c>
       <c r="L26" t="n">
-        <v>8.57</v>
+        <v>9.84</v>
       </c>
       <c r="M26" t="n">
         <v>1.17</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="O26" t="n">
         <v>5.05</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43433</v>
+        <v>43434</v>
       </c>
       <c r="H27" t="n">
-        <v>2656.5</v>
+        <v>2678</v>
       </c>
       <c r="I27" t="n">
         <v>2662.212434754151</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.35</v>
+        <v>-2.17</v>
       </c>
       <c r="L27" t="n">
         <v>4.48</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43469</v>
+        <v>43472</v>
       </c>
       <c r="H28" t="n">
-        <v>2666.5</v>
+        <v>2593</v>
       </c>
       <c r="I28" t="n">
         <v>2606.839582732764</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.43</v>
+        <v>-3.17</v>
       </c>
       <c r="L28" t="n">
-        <v>2.76</v>
+        <v>3.68</v>
       </c>
       <c r="M28" t="n">
         <v>2.63</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.59</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H29" t="n">
-        <v>2643.5</v>
+        <v>2701.5</v>
       </c>
       <c r="I29" t="n">
         <v>2662.648694918326</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.95</v>
+        <v>-4.18</v>
       </c>
       <c r="L29" t="n">
-        <v>3.34</v>
+        <v>4.74</v>
       </c>
       <c r="M29" t="n">
         <v>0.41</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H30" t="n">
-        <v>2850.5</v>
+        <v>2801.5</v>
       </c>
       <c r="I30" t="n">
         <v>2832.485466196779</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K30" t="n">
-        <v>5.52</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
         <v>2.02</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.32</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43691</v>
+        <v>43693</v>
       </c>
       <c r="H31" t="n">
-        <v>2647</v>
+        <v>2683</v>
       </c>
       <c r="I31" t="n">
         <v>2654.183589028818</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K31" t="n">
-        <v>5.51</v>
+        <v>4.23</v>
       </c>
       <c r="L31" t="n">
         <v>2.18</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.03</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43832</v>
+        <v>43833</v>
       </c>
       <c r="H32" t="n">
-        <v>3044</v>
+        <v>2996</v>
       </c>
       <c r="I32" t="n">
         <v>3037.768503888856</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K32" t="n">
-        <v>13.46</v>
+        <v>11.67</v>
       </c>
       <c r="L32" t="n">
         <v>3.26</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.68</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43862</v>
+        <v>43864</v>
       </c>
       <c r="H33" t="n">
-        <v>3065.5</v>
+        <v>3203.5</v>
       </c>
       <c r="I33" t="n">
         <v>3111.210707347322</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.32</v>
+        <v>-6.93</v>
       </c>
       <c r="L33" t="n">
-        <v>5.47</v>
+        <v>7.91</v>
       </c>
       <c r="M33" t="n">
         <v>0.6</v>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
         <v>-1.58</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H34" t="n">
-        <v>2989.5</v>
+        <v>2907</v>
       </c>
       <c r="I34" t="n">
         <v>2908.333010352766</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.68</v>
+        <v>-9.26</v>
       </c>
       <c r="L34" t="n">
-        <v>7.65</v>
+        <v>9.58</v>
       </c>
       <c r="M34" t="n">
         <v>0.45</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43945</v>
+        <v>43948</v>
       </c>
       <c r="H35" t="n">
-        <v>2385</v>
+        <v>2444</v>
       </c>
       <c r="I35" t="n">
         <v>2426.54255693332</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
-        <v>17.96</v>
+        <v>15.93</v>
       </c>
       <c r="L35" t="n">
         <v>3.49</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44075</v>
+        <v>44076</v>
       </c>
       <c r="H36" t="n">
-        <v>2885.5</v>
+        <v>2809.5</v>
       </c>
       <c r="I36" t="n">
         <v>2822.569865519888</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K36" t="n">
-        <v>18.06</v>
+        <v>14.95</v>
       </c>
       <c r="L36" t="n">
         <v>5.77</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44160</v>
+        <v>44161</v>
       </c>
       <c r="H37" t="n">
-        <v>2976</v>
+        <v>3052</v>
       </c>
       <c r="I37" t="n">
         <v>3021.53557380861</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.93</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L37" t="n">
         <v>9.699999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.63</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H38" t="n">
-        <v>3847.5</v>
+        <v>3705</v>
       </c>
       <c r="I38" t="n">
         <v>3769.743826433053</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K38" t="n">
-        <v>26.06</v>
+        <v>21.4</v>
       </c>
       <c r="L38" t="n">
         <v>2.44</v>
@@ -2607,7 +3062,7 @@
         <v>1.61</v>
       </c>
       <c r="N38" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
         <v>2.55</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.25</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44313</v>
+        <v>44314</v>
       </c>
       <c r="H39" t="n">
-        <v>3692</v>
+        <v>3793.5</v>
       </c>
       <c r="I39" t="n">
         <v>3741.06877941075</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K39" t="n">
-        <v>0.35</v>
+        <v>-2.39</v>
       </c>
       <c r="L39" t="n">
         <v>4.9</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44385</v>
+        <v>44386</v>
       </c>
       <c r="H40" t="n">
-        <v>3976.5</v>
+        <v>3897</v>
       </c>
       <c r="I40" t="n">
         <v>3921.819542274348</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K40" t="n">
-        <v>4.82</v>
+        <v>2.73</v>
       </c>
       <c r="L40" t="n">
         <v>2.72</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.11</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H41" t="n">
-        <v>3715.5</v>
+        <v>3816.5</v>
       </c>
       <c r="I41" t="n">
         <v>3793.00665378449</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>4.66</v>
+        <v>2.07</v>
       </c>
       <c r="L41" t="n">
         <v>2.1</v>
@@ -2778,7 +3269,7 @@
         <v>1.15</v>
       </c>
       <c r="N41" t="n">
-        <v>1.76</v>
+        <v>2.72</v>
       </c>
       <c r="O41" t="n">
         <v>-2</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.42</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H42" t="n">
-        <v>3683</v>
+        <v>3609</v>
       </c>
       <c r="I42" t="n">
         <v>3658.122446285442</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.5</v>
+        <v>-5.44</v>
       </c>
       <c r="L42" t="n">
-        <v>4.56</v>
+        <v>5.74</v>
       </c>
       <c r="M42" t="n">
         <v>2.65</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.6</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H43" t="n">
-        <v>3208</v>
+        <v>3275.5</v>
       </c>
       <c r="I43" t="n">
         <v>3260.680417644991</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>11.11</v>
+        <v>9.24</v>
       </c>
       <c r="L43" t="n">
         <v>4.31</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.27</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44622</v>
+        <v>44623</v>
       </c>
       <c r="H44" t="n">
-        <v>3289</v>
+        <v>3215.5</v>
       </c>
       <c r="I44" t="n">
         <v>3275.922386805586</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K44" t="n">
-        <v>0.41</v>
+        <v>-1.83</v>
       </c>
       <c r="L44" t="n">
         <v>2.64</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>10.96</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H45" t="n">
-        <v>3368.5</v>
+        <v>3481.5</v>
       </c>
       <c r="I45" t="n">
         <v>3456.508253869269</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.76</v>
+        <v>-8.27</v>
       </c>
       <c r="L45" t="n">
-        <v>5.97</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="O45" t="n">
         <v>-2.23</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H46" t="n">
-        <v>3534</v>
+        <v>3410.5</v>
       </c>
       <c r="I46" t="n">
         <v>3492.815831414158</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K46" t="n">
-        <v>1.51</v>
+        <v>-2.04</v>
       </c>
       <c r="L46" t="n">
         <v>2.48</v>
@@ -3063,7 +3614,7 @@
         <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.85</v>
+        <v>3.49</v>
       </c>
       <c r="O46" t="n">
         <v>3.35</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.91</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44706</v>
+        <v>44707</v>
       </c>
       <c r="H47" t="n">
-        <v>3698</v>
+        <v>3762</v>
       </c>
       <c r="I47" t="n">
         <v>3761.973253237428</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.43</v>
+        <v>-10.31</v>
       </c>
       <c r="L47" t="n">
         <v>10.79</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="H48" t="n">
-        <v>3788</v>
+        <v>3763</v>
       </c>
       <c r="I48" t="n">
         <v>3763.643675695552</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="L48" t="n">
         <v>7.32</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.6</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44867</v>
+        <v>44868</v>
       </c>
       <c r="H49" t="n">
-        <v>3644.5</v>
+        <v>3680</v>
       </c>
       <c r="I49" t="n">
         <v>3674.79331270684</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K49" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="L49" t="n">
         <v>7.08</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.45</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H50" t="n">
-        <v>3530</v>
+        <v>3462</v>
       </c>
       <c r="I50" t="n">
         <v>3473.276895945912</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.08</v>
+        <v>-5.92</v>
       </c>
       <c r="L50" t="n">
-        <v>5.3</v>
+        <v>6.21</v>
       </c>
       <c r="M50" t="n">
         <v>0.49</v>
       </c>
       <c r="N50" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="O50" t="n">
         <v>0.97</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.26</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H51" t="n">
-        <v>3625.5</v>
+        <v>3839.5</v>
       </c>
       <c r="I51" t="n">
         <v>3646.700489227315</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.72</v>
+        <v>-10.9</v>
       </c>
       <c r="L51" t="n">
-        <v>5.36</v>
+        <v>12.55</v>
       </c>
       <c r="M51" t="n">
-        <v>0.51</v>
+        <v>3.57</v>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>5.9</v>
       </c>
       <c r="O51" t="n">
         <v>-1.93</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.95</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H52" t="n">
-        <v>3755</v>
+        <v>3550</v>
       </c>
       <c r="I52" t="n">
         <v>3621.656965907907</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.2</v>
+        <v>-7.54</v>
       </c>
       <c r="L52" t="n">
-        <v>5</v>
+        <v>7.89</v>
       </c>
       <c r="M52" t="n">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>5.46</v>
       </c>
       <c r="O52" t="n">
         <v>5.9</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.82</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H53" t="n">
-        <v>3788.5</v>
+        <v>3895</v>
       </c>
       <c r="I53" t="n">
         <v>3845.176062630936</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.72</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>8.390000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="M53" t="n">
         <v>0.59</v>
       </c>
       <c r="N53" t="n">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="O53" t="n">
         <v>-5.46</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.83</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45093</v>
+        <v>45096</v>
       </c>
       <c r="H54" t="n">
-        <v>4527</v>
+        <v>4483.5</v>
       </c>
       <c r="I54" t="n">
         <v>4490.212670614162</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K54" t="n">
-        <v>16.23</v>
+        <v>15.11</v>
       </c>
       <c r="L54" t="n">
         <v>2.64</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.95</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45111</v>
+        <v>45112</v>
       </c>
       <c r="H55" t="n">
-        <v>4511</v>
+        <v>4769</v>
       </c>
       <c r="I55" t="n">
         <v>4705.651566704525</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.61</v>
+        <v>-6.37</v>
       </c>
       <c r="L55" t="n">
-        <v>3.11</v>
+        <v>6.59</v>
       </c>
       <c r="M55" t="n">
         <v>0.59</v>
       </c>
       <c r="N55" t="n">
-        <v>2.12</v>
+        <v>5.72</v>
       </c>
       <c r="O55" t="n">
         <v>-0.96</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45142</v>
+        <v>45145</v>
       </c>
       <c r="H56" t="n">
-        <v>4595.5</v>
+        <v>4554.5</v>
       </c>
       <c r="I56" t="n">
         <v>4561.957115161011</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.64</v>
+        <v>-4.5</v>
       </c>
       <c r="L56" t="n">
         <v>5.25</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.97</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45182</v>
+        <v>45183</v>
       </c>
       <c r="H57" t="n">
-        <v>4689.5</v>
+        <v>4725</v>
       </c>
       <c r="I57" t="n">
         <v>4709.594638840132</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.96</v>
+        <v>-3.74</v>
       </c>
       <c r="L57" t="n">
-        <v>3.85</v>
+        <v>4.03</v>
       </c>
       <c r="M57" t="n">
         <v>0.78</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.85</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H58" t="n">
-        <v>7986</v>
+        <v>7714</v>
       </c>
       <c r="I58" t="n">
         <v>7748.677734135632</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K58" t="n">
-        <v>69.02</v>
+        <v>63.26</v>
       </c>
       <c r="L58" t="n">
         <v>1.19</v>
@@ -3747,7 +4442,7 @@
         <v>2.5</v>
       </c>
       <c r="N58" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="O58" t="n">
         <v>0.76</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.66</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="H59" t="n">
-        <v>8393</v>
+        <v>8659.5</v>
       </c>
       <c r="I59" t="n">
         <v>8451.848416338511</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.800000000000001</v>
+        <v>-12.26</v>
       </c>
       <c r="L59" t="n">
-        <v>9.75</v>
+        <v>13.44</v>
       </c>
       <c r="M59" t="n">
         <v>0.58</v>
       </c>
       <c r="N59" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="O59" t="n">
         <v>-3.41</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H60" t="n">
-        <v>9150.5</v>
+        <v>9031.5</v>
       </c>
       <c r="I60" t="n">
         <v>9102.205985468061</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K60" t="n">
-        <v>5.67</v>
+        <v>4.3</v>
       </c>
       <c r="L60" t="n">
         <v>8.66</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45526</v>
+        <v>45527</v>
       </c>
       <c r="H61" t="n">
-        <v>9669</v>
+        <v>10149</v>
       </c>
       <c r="I61" t="n">
         <v>9757.936567273277</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.06</v>
+        <v>-12.37</v>
       </c>
       <c r="L61" t="n">
-        <v>8.1</v>
+        <v>12.78</v>
       </c>
       <c r="M61" t="n">
         <v>1.86</v>
       </c>
       <c r="N61" t="n">
-        <v>2.97</v>
+        <v>4.96</v>
       </c>
       <c r="O61" t="n">
         <v>-1.3</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H62" t="n">
-        <v>11857</v>
+        <v>11514.5</v>
       </c>
       <c r="I62" t="n">
         <v>11632.80048719435</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K62" t="n">
-        <v>16.83</v>
+        <v>13.45</v>
       </c>
       <c r="L62" t="n">
         <v>4.58</v>
       </c>
       <c r="M62" t="n">
-        <v>0.92</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="O62" t="n">
         <v>4.96</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.83</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H63" t="n">
-        <v>8629</v>
+        <v>8929.5</v>
       </c>
       <c r="I63" t="n">
         <v>8648.357196495523</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K63" t="n">
-        <v>25.06</v>
+        <v>22.45</v>
       </c>
       <c r="L63" t="n">
         <v>1.9</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45713</v>
+        <v>45715</v>
       </c>
       <c r="H64" t="n">
-        <v>8210</v>
+        <v>8029</v>
       </c>
       <c r="I64" t="n">
         <v>8158.347407668156</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.06</v>
+        <v>-10.08</v>
       </c>
       <c r="L64" t="n">
-        <v>8.890000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="M64" t="n">
         <v>0.93</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H65" t="n">
-        <v>7724</v>
+        <v>7868.5</v>
       </c>
       <c r="I65" t="n">
         <v>7830.111222793623</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
         <v>2.2</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>7.45</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H66" t="n">
-        <v>7495</v>
+        <v>7126</v>
       </c>
       <c r="I66" t="n">
         <v>7390.668653660916</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.75</v>
+        <v>-9.44</v>
       </c>
       <c r="L66" t="n">
-        <v>5.41</v>
+        <v>12.13</v>
       </c>
       <c r="M66" t="n">
-        <v>3.14</v>
+        <v>5.01</v>
       </c>
       <c r="N66" t="n">
-        <v>2.87</v>
+        <v>4.92</v>
       </c>
       <c r="O66" t="n">
         <v>1.87</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>9.15</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H67" t="n">
-        <v>7577</v>
+        <v>7798</v>
       </c>
       <c r="I67" t="n">
         <v>7778.067186629966</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.33</v>
+        <v>-9.43</v>
       </c>
       <c r="L67" t="n">
-        <v>6.48</v>
+        <v>10.04</v>
       </c>
       <c r="M67" t="n">
-        <v>1.94</v>
+        <v>2.98</v>
       </c>
       <c r="N67" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="O67" t="n">
         <v>-4.92</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H68" t="n">
-        <v>8285</v>
+        <v>8067</v>
       </c>
       <c r="I68" t="n">
         <v>8101.902120530101</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K68" t="n">
-        <v>6.25</v>
+        <v>3.45</v>
       </c>
       <c r="L68" t="n">
         <v>4.8</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>6.28</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="H69" t="n">
-        <v>8213.5</v>
+        <v>8588.5</v>
       </c>
       <c r="I69" t="n">
         <v>8421.156157532436</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.82</v>
+        <v>-6.46</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>6.97</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5</v>
+        <v>2.27</v>
       </c>
       <c r="N69" t="n">
-        <v>2.76</v>
+        <v>4.57</v>
       </c>
       <c r="O69" t="n">
         <v>-2.63</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.86</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="H70" t="n">
-        <v>8717.5</v>
+        <v>8678.5</v>
       </c>
       <c r="I70" t="n">
         <v>8699.739543518695</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K70" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="L70" t="n">
         <v>2.19</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.37</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H71" t="n">
-        <v>9048</v>
+        <v>9164</v>
       </c>
       <c r="I71" t="n">
         <v>9115.552441992706</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.26</v>
+        <v>-5.59</v>
       </c>
       <c r="L71" t="n">
         <v>6.43</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.22</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H72" t="n">
-        <v>9429.5</v>
+        <v>9180</v>
       </c>
       <c r="I72" t="n">
         <v>9242.621457663496</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K72" t="n">
-        <v>2.9</v>
+        <v>0.17</v>
       </c>
       <c r="L72" t="n">
         <v>4.68</v>
@@ -4545,7 +5408,7 @@
         <v>0.41</v>
       </c>
       <c r="N72" t="n">
-        <v>2.03</v>
+        <v>2.65</v>
       </c>
       <c r="O72" t="n">
         <v>1.28</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.75</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H73" t="n">
-        <v>9590</v>
+        <v>9774</v>
       </c>
       <c r="I73" t="n">
         <v>9740.557337888462</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K73" t="n">
-        <v>-4.47</v>
+        <v>-6.47</v>
       </c>
       <c r="L73" t="n">
         <v>8.289999999999999</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.76</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H74" t="n">
-        <v>9816</v>
+        <v>9383</v>
       </c>
       <c r="I74" t="n">
         <v>9466.386184570219</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K74" t="n">
-        <v>0.43</v>
+        <v>-4</v>
       </c>
       <c r="L74" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="M74" t="n">
         <v>2.65</v>
       </c>
       <c r="N74" t="n">
-        <v>2.52</v>
+        <v>4.41</v>
       </c>
       <c r="O74" t="n">
         <v>1.92</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>9.24</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H75" t="n">
-        <v>9517</v>
+        <v>9813.5</v>
       </c>
       <c r="I75" t="n">
         <v>9545.727857591824</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.43</v>
+        <v>-4.59</v>
       </c>
       <c r="L75" t="n">
-        <v>3.02</v>
+        <v>4.91</v>
       </c>
       <c r="M75" t="n">
         <v>3.49</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>11.15</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="H76" t="n">
-        <v>10025</v>
+        <v>9750</v>
       </c>
       <c r="I76" t="n">
         <v>9919.142936446911</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K76" t="n">
-        <v>2.16</v>
+        <v>-0.65</v>
       </c>
       <c r="L76" t="n">
         <v>4.67</v>
       </c>
       <c r="M76" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="N76" t="n">
         <v>3.22</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>7.52</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="H77" t="n">
-        <v>10156</v>
+        <v>10381</v>
       </c>
       <c r="I77" t="n">
         <v>10304.62524710825</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.16</v>
+        <v>-6.47</v>
       </c>
       <c r="L77" t="n">
-        <v>5.62</v>
+        <v>7.1</v>
       </c>
       <c r="M77" t="n">
         <v>1.35</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>8.15</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H78" t="n">
-        <v>11678</v>
+        <v>11424</v>
       </c>
       <c r="I78" t="n">
         <v>11615.39604980262</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K78" t="n">
-        <v>12.49</v>
+        <v>10.05</v>
       </c>
       <c r="L78" t="n">
         <v>3.38</v>
@@ -4887,7 +5822,7 @@
         <v>1.62</v>
       </c>
       <c r="N78" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O78" t="n">
         <v>2.22</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>30</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="11">
@@ -9965,7 +10920,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -9975,7 +10930,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -9985,7 +10940,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37.7</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="14">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.12</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69.02</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.8</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.8</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.48</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.07</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="25">
@@ -10105,7 +11060,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="26">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.11</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="27">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
